--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.92710656308841</v>
+        <v>4.538154816501867</v>
       </c>
       <c r="D2" t="n">
-        <v>28.04604520254667</v>
+        <v>4.557482345413834</v>
       </c>
       <c r="E2" t="n">
-        <v>6.185307897633098</v>
+        <v>1.005112533365379</v>
       </c>
       <c r="F2" t="n">
-        <v>6.018006842792285</v>
+        <v>0.9779261119537465</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.46680811309792</v>
+        <v>3.650856318378411</v>
       </c>
       <c r="D3" t="n">
-        <v>22.49738812361343</v>
+        <v>3.655825570087182</v>
       </c>
       <c r="E3" t="n">
-        <v>6.185307897633098</v>
+        <v>1.005112533365379</v>
       </c>
       <c r="F3" t="n">
-        <v>6.018006842792285</v>
+        <v>0.9779261119537465</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.08562462759874</v>
+        <v>4.888914001984795</v>
       </c>
       <c r="D4" t="n">
-        <v>29.76489501865804</v>
+        <v>4.836795440531931</v>
       </c>
       <c r="E4" t="n">
-        <v>6.185307897633098</v>
+        <v>1.005112533365379</v>
       </c>
       <c r="F4" t="n">
-        <v>6.018006842792285</v>
+        <v>0.9779261119537465</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.33284928068391</v>
+        <v>2.004088008111136</v>
       </c>
       <c r="D5" t="n">
-        <v>12.73411264782683</v>
+        <v>2.069293305271861</v>
       </c>
       <c r="E5" t="n">
-        <v>6.185307897633098</v>
+        <v>1.005112533365379</v>
       </c>
       <c r="F5" t="n">
-        <v>6.018006842792285</v>
+        <v>0.9779261119537465</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.29905235885211</v>
+        <v>3.461096008313468</v>
       </c>
       <c r="D6" t="n">
-        <v>20.89252452867753</v>
+        <v>3.395035235910098</v>
       </c>
       <c r="E6" t="n">
-        <v>6.185307897633098</v>
+        <v>1.005112533365379</v>
       </c>
       <c r="F6" t="n">
-        <v>6.018006842792285</v>
+        <v>0.9779261119537465</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
